--- a/analyse-statistique-inferentielle/analyse-statistique.xlsx
+++ b/analyse-statistique-inferentielle/analyse-statistique.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr codeName="ThisWorkbook" showPivotChartFilter="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,6 +10,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="25" documentId="8_{2FDA18AA-9BE0-4D3C-8102-2BFCEF67CDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BD61B6A-686C-4A8E-BF5C-F85917D77103}"/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="6100" yWindow="4080" windowWidth="7500" windowHeight="6000" tabRatio="704" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19387,6 +19389,7 @@
       <c r="G58" s="48"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="4">
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="I41:K41"/>
@@ -31073,6 +31076,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31440,6 +31444,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="12">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A20:B20"/>
@@ -31620,6 +31625,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
     <mergeCell ref="B6:D6"/>
   </mergeCells>
@@ -31725,6 +31731,7 @@
       <c r="B35" s="151"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:I5"/>
@@ -32094,6 +32101,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="4">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A18:B18"/>
@@ -32258,6 +32266,7 @@
       <c r="J18" s="150"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="10">
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A8:C8"/>
@@ -39805,6 +39814,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="2">
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="A1:J1"/>
@@ -41039,6 +41049,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B153">
     <sortCondition ref="B4:B153"/>
   </sortState>
@@ -41800,6 +41811,7 @@
     <row r="58" spans="3:11" ht="13" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="3:11" ht="13" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="13">
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="B12:E12"/>
@@ -42796,6 +42808,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="1" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" insertHyperlinks="1" deleteColumns="1" deleteRows="1" selectLockedCells="0" selectUnlockedCells="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
